--- a/2026-EgoAnchor/material/old3/GPT-5.6_Thinking_Experiment3_Synthetic_VSCodeSafe.xlsx
+++ b/2026-EgoAnchor/material/old3/GPT-5.6_Thinking_Experiment3_Synthetic_VSCodeSafe.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="6"/>
+    <workbookView windowWidth="25600" windowHeight="12080" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -2847,6 +2847,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF22313F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>方法</t>
     </r>
     <r>
@@ -2903,6 +2909,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF22313F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>我更相信方法</t>
     </r>
     <r>
@@ -4253,7 +4265,7 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4402,7 +4414,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4666,6 +4678,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="4" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5481,12 +5496,12 @@
       </c>
     </row>
     <row r="19" ht="64" customHeight="1" spans="1:5">
-      <c r="A19" s="90" t="s">
+      <c r="A19" s="91" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="20" ht="64" customHeight="1" spans="1:5">
-      <c r="A20" s="90" t="s">
+      <c r="A20" s="91" t="s">
         <v>52</v>
       </c>
     </row>
@@ -5503,7 +5518,7 @@
       </c>
     </row>
     <row r="23" ht="76" customHeight="1" spans="1:5">
-      <c r="A23" s="95" t="s">
+      <c r="A23" s="96" t="s">
         <v>54</v>
       </c>
     </row>
@@ -5515,7 +5530,7 @@
       <c r="E24" s="73"/>
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:5">
-      <c r="A25" s="90" t="s">
+      <c r="A25" s="91" t="s">
         <v>55</v>
       </c>
     </row>
@@ -5581,7 +5596,7 @@
       <c r="A5" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="123" t="s">
+      <c r="B5" s="124" t="s">
         <v>63</v>
       </c>
       <c r="C5" s="79" t="s">
@@ -5595,7 +5610,7 @@
       <c r="A6" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="124" t="s">
+      <c r="B6" s="125" t="s">
         <v>63</v>
       </c>
       <c r="C6" s="73" t="s">
@@ -5609,7 +5624,7 @@
       <c r="A7" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="124" t="s">
+      <c r="B7" s="125" t="s">
         <v>63</v>
       </c>
       <c r="C7" s="73" t="s">
@@ -5623,7 +5638,7 @@
       <c r="A8" s="81" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="124" t="s">
+      <c r="B8" s="125" t="s">
         <v>63</v>
       </c>
       <c r="C8" s="73" t="s">
@@ -5637,7 +5652,7 @@
       <c r="A9" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="124" t="s">
+      <c r="B9" s="125" t="s">
         <v>63</v>
       </c>
       <c r="C9" s="73" t="s">
@@ -5651,7 +5666,7 @@
       <c r="A10" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="124" t="s">
+      <c r="B10" s="125" t="s">
         <v>63</v>
       </c>
       <c r="C10" s="73" t="s">
@@ -5665,7 +5680,7 @@
       <c r="A11" s="81" t="s">
         <v>79</v>
       </c>
-      <c r="B11" s="125" t="s">
+      <c r="B11" s="126" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="73" t="s">
@@ -5679,7 +5694,7 @@
       <c r="A12" s="81" t="s">
         <v>83</v>
       </c>
-      <c r="B12" s="124" t="s">
+      <c r="B12" s="125" t="s">
         <v>63</v>
       </c>
       <c r="C12" s="73" t="s">
@@ -5693,7 +5708,7 @@
       <c r="A13" s="81" t="s">
         <v>86</v>
       </c>
-      <c r="B13" s="124" t="s">
+      <c r="B13" s="125" t="s">
         <v>63</v>
       </c>
       <c r="C13" s="73" t="s">
@@ -5707,7 +5722,7 @@
       <c r="A14" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="B14" s="113" t="s">
+      <c r="B14" s="114" t="s">
         <v>89</v>
       </c>
       <c r="C14" s="73" t="s">
@@ -5721,7 +5736,7 @@
       <c r="A15" s="81" t="s">
         <v>92</v>
       </c>
-      <c r="B15" s="124" t="s">
+      <c r="B15" s="125" t="s">
         <v>63</v>
       </c>
       <c r="C15" s="73" t="s">
@@ -5735,7 +5750,7 @@
       <c r="A16" s="81" t="s">
         <v>95</v>
       </c>
-      <c r="B16" s="125" t="s">
+      <c r="B16" s="126" t="s">
         <v>80</v>
       </c>
       <c r="C16" s="73" t="s">
@@ -5749,7 +5764,7 @@
       <c r="A17" s="81" t="s">
         <v>97</v>
       </c>
-      <c r="B17" s="126" t="s">
+      <c r="B17" s="127" t="s">
         <v>98</v>
       </c>
       <c r="C17" s="73" t="s">
@@ -5763,7 +5778,7 @@
       <c r="A18" s="81" t="s">
         <v>101</v>
       </c>
-      <c r="B18" s="126" t="s">
+      <c r="B18" s="127" t="s">
         <v>102</v>
       </c>
       <c r="C18" s="73" t="s">
@@ -5777,7 +5792,7 @@
       <c r="A19" s="83" t="s">
         <v>105</v>
       </c>
-      <c r="B19" s="127" t="s">
+      <c r="B19" s="128" t="s">
         <v>106</v>
       </c>
       <c r="C19" s="84" t="s">
@@ -6057,7 +6072,7 @@
       <c r="C16" s="87" t="s">
         <v>158</v>
       </c>
-      <c r="D16" s="87" t="s">
+      <c r="D16" s="89" t="s">
         <v>159</v>
       </c>
       <c r="E16" s="87" t="s">
@@ -6106,89 +6121,89 @@
       </c>
     </row>
     <row r="18" ht="62" customHeight="1" spans="1:9">
-      <c r="A18" s="89" t="s">
+      <c r="A18" s="90" t="s">
         <v>169</v>
       </c>
-      <c r="B18" s="90" t="s">
+      <c r="B18" s="91" t="s">
         <v>170</v>
       </c>
-      <c r="C18" s="90" t="s">
+      <c r="C18" s="91" t="s">
         <v>171</v>
       </c>
-      <c r="D18" s="90" t="s">
+      <c r="D18" s="91" t="s">
         <v>172</v>
       </c>
-      <c r="E18" s="90" t="s">
+      <c r="E18" s="91" t="s">
         <v>151</v>
       </c>
-      <c r="F18" s="90" t="s">
+      <c r="F18" s="91" t="s">
         <v>173</v>
       </c>
-      <c r="G18" s="90" t="s">
+      <c r="G18" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H18" s="90" t="s">
+      <c r="H18" s="91" t="s">
         <v>174</v>
       </c>
-      <c r="I18" s="91" t="s">
+      <c r="I18" s="92" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="19" ht="62" customHeight="1" spans="1:9">
-      <c r="A19" s="92" t="s">
+      <c r="A19" s="93" t="s">
         <v>176</v>
       </c>
-      <c r="B19" s="93" t="s">
+      <c r="B19" s="94" t="s">
         <v>177</v>
       </c>
-      <c r="C19" s="93" t="s">
+      <c r="C19" s="94" t="s">
         <v>178</v>
       </c>
-      <c r="D19" s="93" t="s">
+      <c r="D19" s="94" t="s">
         <v>179</v>
       </c>
-      <c r="E19" s="93" t="s">
+      <c r="E19" s="94" t="s">
         <v>180</v>
       </c>
-      <c r="F19" s="93" t="s">
+      <c r="F19" s="94" t="s">
         <v>181</v>
       </c>
-      <c r="G19" s="93" t="s">
+      <c r="G19" s="94" t="s">
         <v>182</v>
       </c>
-      <c r="H19" s="93" t="s">
+      <c r="H19" s="94" t="s">
         <v>183</v>
       </c>
-      <c r="I19" s="94" t="s">
+      <c r="I19" s="95" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="20" ht="62" customHeight="1" spans="1:9">
-      <c r="A20" s="92" t="s">
+      <c r="A20" s="93" t="s">
         <v>185</v>
       </c>
-      <c r="B20" s="93" t="s">
+      <c r="B20" s="94" t="s">
         <v>186</v>
       </c>
-      <c r="C20" s="93" t="s">
+      <c r="C20" s="94" t="s">
         <v>187</v>
       </c>
-      <c r="D20" s="93" t="s">
+      <c r="D20" s="94" t="s">
         <v>188</v>
       </c>
-      <c r="E20" s="93" t="s">
+      <c r="E20" s="94" t="s">
         <v>189</v>
       </c>
-      <c r="F20" s="93" t="s">
+      <c r="F20" s="94" t="s">
         <v>190</v>
       </c>
-      <c r="G20" s="93" t="s">
+      <c r="G20" s="94" t="s">
         <v>182</v>
       </c>
-      <c r="H20" s="93" t="s">
+      <c r="H20" s="94" t="s">
         <v>183</v>
       </c>
-      <c r="I20" s="94" t="s">
+      <c r="I20" s="95" t="s">
         <v>191</v>
       </c>
     </row>
@@ -6251,118 +6266,118 @@
       </c>
     </row>
     <row r="23" ht="62" customHeight="1" spans="1:9">
-      <c r="A23" s="92" t="s">
+      <c r="A23" s="93" t="s">
         <v>204</v>
       </c>
-      <c r="B23" s="93" t="s">
+      <c r="B23" s="94" t="s">
         <v>205</v>
       </c>
-      <c r="C23" s="93" t="s">
+      <c r="C23" s="94" t="s">
         <v>206</v>
       </c>
-      <c r="D23" s="93" t="s">
+      <c r="D23" s="94" t="s">
         <v>207</v>
       </c>
-      <c r="E23" s="93" t="s">
+      <c r="E23" s="94" t="s">
         <v>208</v>
       </c>
-      <c r="F23" s="93" t="s">
+      <c r="F23" s="94" t="s">
         <v>209</v>
       </c>
-      <c r="G23" s="93" t="s">
+      <c r="G23" s="94" t="s">
         <v>182</v>
       </c>
-      <c r="H23" s="93" t="s">
+      <c r="H23" s="94" t="s">
         <v>210</v>
       </c>
-      <c r="I23" s="94" t="s">
+      <c r="I23" s="95" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="24" ht="62" customHeight="1" spans="1:9">
-      <c r="A24" s="92" t="s">
+      <c r="A24" s="93" t="s">
         <v>212</v>
       </c>
-      <c r="B24" s="93" t="s">
+      <c r="B24" s="94" t="s">
         <v>213</v>
       </c>
-      <c r="C24" s="93" t="s">
+      <c r="C24" s="94" t="s">
         <v>214</v>
       </c>
-      <c r="D24" s="93" t="s">
+      <c r="D24" s="94" t="s">
         <v>215</v>
       </c>
-      <c r="E24" s="93" t="s">
+      <c r="E24" s="94" t="s">
         <v>216</v>
       </c>
-      <c r="F24" s="93" t="s">
+      <c r="F24" s="94" t="s">
         <v>217</v>
       </c>
-      <c r="G24" s="93" t="s">
+      <c r="G24" s="94" t="s">
         <v>182</v>
       </c>
-      <c r="H24" s="93" t="s">
+      <c r="H24" s="94" t="s">
         <v>210</v>
       </c>
-      <c r="I24" s="94" t="s">
+      <c r="I24" s="95" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="25" ht="62" customHeight="1" spans="1:9">
-      <c r="A25" s="92" t="s">
+      <c r="A25" s="93" t="s">
         <v>219</v>
       </c>
-      <c r="B25" s="93" t="s">
+      <c r="B25" s="94" t="s">
         <v>220</v>
       </c>
-      <c r="C25" s="93" t="s">
+      <c r="C25" s="94" t="s">
         <v>221</v>
       </c>
-      <c r="D25" s="93" t="s">
+      <c r="D25" s="94" t="s">
         <v>222</v>
       </c>
-      <c r="E25" s="93" t="s">
+      <c r="E25" s="94" t="s">
         <v>223</v>
       </c>
-      <c r="F25" s="93" t="s">
+      <c r="F25" s="94" t="s">
         <v>224</v>
       </c>
-      <c r="G25" s="93" t="s">
+      <c r="G25" s="94" t="s">
         <v>182</v>
       </c>
-      <c r="H25" s="93" t="s">
+      <c r="H25" s="94" t="s">
         <v>210</v>
       </c>
-      <c r="I25" s="94" t="s">
+      <c r="I25" s="95" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="26" ht="62" customHeight="1" spans="1:9">
-      <c r="A26" s="92" t="s">
+      <c r="A26" s="93" t="s">
         <v>226</v>
       </c>
-      <c r="B26" s="93" t="s">
+      <c r="B26" s="94" t="s">
         <v>227</v>
       </c>
-      <c r="C26" s="93" t="s">
+      <c r="C26" s="94" t="s">
         <v>228</v>
       </c>
-      <c r="D26" s="93" t="s">
+      <c r="D26" s="94" t="s">
         <v>229</v>
       </c>
-      <c r="E26" s="93" t="s">
+      <c r="E26" s="94" t="s">
         <v>230</v>
       </c>
-      <c r="F26" s="93" t="s">
+      <c r="F26" s="94" t="s">
         <v>231</v>
       </c>
-      <c r="G26" s="93" t="s">
+      <c r="G26" s="94" t="s">
         <v>182</v>
       </c>
-      <c r="H26" s="93" t="s">
+      <c r="H26" s="94" t="s">
         <v>183</v>
       </c>
-      <c r="I26" s="94" t="s">
+      <c r="I26" s="95" t="s">
         <v>191</v>
       </c>
     </row>
@@ -6425,21 +6440,21 @@
       </c>
     </row>
     <row r="29" ht="52" spans="1:9">
-      <c r="A29" s="95" t="s">
+      <c r="A29" s="96" t="s">
         <v>244</v>
       </c>
-      <c r="B29" s="95" t="s">
+      <c r="B29" s="96" t="s">
         <v>245</v>
       </c>
-      <c r="C29" s="95" t="s">
+      <c r="C29" s="96" t="s">
         <v>246</v>
       </c>
-      <c r="D29" s="95"/>
-      <c r="E29" s="95"/>
-      <c r="F29" s="95"/>
-      <c r="G29" s="95"/>
-      <c r="H29" s="95"/>
-      <c r="I29" s="95"/>
+      <c r="D29" s="96"/>
+      <c r="E29" s="96"/>
+      <c r="F29" s="96"/>
+      <c r="G29" s="96"/>
+      <c r="H29" s="96"/>
+      <c r="I29" s="96"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="73"/>
@@ -6458,21 +6473,21 @@
       </c>
     </row>
     <row r="32" ht="117" spans="1:9">
-      <c r="A32" s="96" t="s">
+      <c r="A32" s="97" t="s">
         <v>248</v>
       </c>
-      <c r="B32" s="96" t="s">
+      <c r="B32" s="97" t="s">
         <v>249</v>
       </c>
-      <c r="C32" s="96" t="s">
+      <c r="C32" s="97" t="s">
         <v>250</v>
       </c>
-      <c r="D32" s="96"/>
-      <c r="E32" s="96"/>
-      <c r="F32" s="96"/>
-      <c r="G32" s="96"/>
-      <c r="H32" s="96"/>
-      <c r="I32" s="96"/>
+      <c r="D32" s="97"/>
+      <c r="E32" s="97"/>
+      <c r="F32" s="97"/>
+      <c r="G32" s="97"/>
+      <c r="H32" s="97"/>
+      <c r="I32" s="97"/>
     </row>
     <row r="33" ht="34" customHeight="1" spans="1:9">
       <c r="A33" s="75" t="s">
@@ -6556,7 +6571,7 @@
       <c r="D36" s="87" t="s">
         <v>265</v>
       </c>
-      <c r="E36" s="97" t="s">
+      <c r="E36" s="98" t="s">
         <v>266</v>
       </c>
       <c r="F36" s="88">
@@ -6602,7 +6617,7 @@
       <c r="D38" s="87" t="s">
         <v>272</v>
       </c>
-      <c r="E38" s="97" t="s">
+      <c r="E38" s="98" t="s">
         <v>266</v>
       </c>
       <c r="F38" s="88">
@@ -6636,22 +6651,22 @@
       <c r="I39" s="73"/>
     </row>
     <row r="40" ht="50" customHeight="1" spans="1:9">
-      <c r="A40" s="98" t="s">
+      <c r="A40" s="99" t="s">
         <v>276</v>
       </c>
-      <c r="B40" s="99" t="s">
+      <c r="B40" s="100" t="s">
         <v>277</v>
       </c>
-      <c r="C40" s="99" t="s">
+      <c r="C40" s="100" t="s">
         <v>278</v>
       </c>
-      <c r="D40" s="99" t="s">
+      <c r="D40" s="100" t="s">
         <v>279</v>
       </c>
-      <c r="E40" s="99" t="s">
+      <c r="E40" s="100" t="s">
         <v>259</v>
       </c>
-      <c r="F40" s="100">
+      <c r="F40" s="101">
         <v>2</v>
       </c>
       <c r="G40" s="73"/>
@@ -6659,22 +6674,22 @@
       <c r="I40" s="73"/>
     </row>
     <row r="41" ht="50" customHeight="1" spans="1:9">
-      <c r="A41" s="98" t="s">
+      <c r="A41" s="99" t="s">
         <v>280</v>
       </c>
-      <c r="B41" s="99" t="s">
+      <c r="B41" s="100" t="s">
         <v>277</v>
       </c>
-      <c r="C41" s="99" t="s">
+      <c r="C41" s="100" t="s">
         <v>281</v>
       </c>
-      <c r="D41" s="99" t="s">
+      <c r="D41" s="100" t="s">
         <v>282</v>
       </c>
-      <c r="E41" s="97" t="s">
-        <v>266</v>
-      </c>
-      <c r="F41" s="100">
+      <c r="E41" s="98" t="s">
+        <v>266</v>
+      </c>
+      <c r="F41" s="101">
         <v>7</v>
       </c>
       <c r="G41" s="73"/>
@@ -6682,22 +6697,22 @@
       <c r="I41" s="73"/>
     </row>
     <row r="42" ht="50" customHeight="1" spans="1:9">
-      <c r="A42" s="98" t="s">
+      <c r="A42" s="99" t="s">
         <v>283</v>
       </c>
-      <c r="B42" s="99" t="s">
+      <c r="B42" s="100" t="s">
         <v>277</v>
       </c>
-      <c r="C42" s="99" t="s">
+      <c r="C42" s="100" t="s">
         <v>284</v>
       </c>
-      <c r="D42" s="99" t="s">
+      <c r="D42" s="100" t="s">
         <v>285</v>
       </c>
-      <c r="E42" s="99" t="s">
+      <c r="E42" s="100" t="s">
         <v>259</v>
       </c>
-      <c r="F42" s="100">
+      <c r="F42" s="101">
         <v>11</v>
       </c>
       <c r="G42" s="73"/>
@@ -6705,22 +6720,22 @@
       <c r="I42" s="73"/>
     </row>
     <row r="43" ht="50" customHeight="1" spans="1:9">
-      <c r="A43" s="98" t="s">
+      <c r="A43" s="99" t="s">
         <v>286</v>
       </c>
-      <c r="B43" s="99" t="s">
+      <c r="B43" s="100" t="s">
         <v>277</v>
       </c>
-      <c r="C43" s="99" t="s">
+      <c r="C43" s="100" t="s">
         <v>287</v>
       </c>
-      <c r="D43" s="99" t="s">
+      <c r="D43" s="100" t="s">
         <v>288</v>
       </c>
-      <c r="E43" s="97" t="s">
-        <v>266</v>
-      </c>
-      <c r="F43" s="100">
+      <c r="E43" s="98" t="s">
+        <v>266</v>
+      </c>
+      <c r="F43" s="101">
         <v>16</v>
       </c>
       <c r="G43" s="73"/>
@@ -6728,31 +6743,31 @@
       <c r="I43" s="73"/>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="90" t="s">
+      <c r="A44" s="91" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" s="101" t="s">
+      <c r="A45" s="102" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1" spans="1:9">
-      <c r="A46" s="96" t="s">
+      <c r="A46" s="97" t="s">
         <v>291</v>
       </c>
-      <c r="B46" s="96" t="s">
+      <c r="B46" s="97" t="s">
         <v>292</v>
       </c>
-      <c r="C46" s="96" t="s">
+      <c r="C46" s="97" t="s">
         <v>293</v>
       </c>
-      <c r="D46" s="96"/>
-      <c r="E46" s="96"/>
-      <c r="F46" s="96"/>
-      <c r="G46" s="96"/>
-      <c r="H46" s="96"/>
-      <c r="I46" s="96"/>
+      <c r="D46" s="97"/>
+      <c r="E46" s="97"/>
+      <c r="F46" s="97"/>
+      <c r="G46" s="97"/>
+      <c r="H46" s="97"/>
+      <c r="I46" s="97"/>
     </row>
     <row r="47" ht="32" customHeight="1" spans="1:9">
       <c r="A47" s="75" t="s">
@@ -6764,21 +6779,21 @@
       <c r="C47" s="77" t="s">
         <v>141</v>
       </c>
-      <c r="D47" s="96"/>
-      <c r="E47" s="96"/>
-      <c r="F47" s="96"/>
-      <c r="G47" s="96"/>
-      <c r="H47" s="96"/>
-      <c r="I47" s="96"/>
+      <c r="D47" s="97"/>
+      <c r="E47" s="97"/>
+      <c r="F47" s="97"/>
+      <c r="G47" s="97"/>
+      <c r="H47" s="97"/>
+      <c r="I47" s="97"/>
     </row>
     <row r="48" ht="42" customHeight="1" spans="1:9">
-      <c r="A48" s="102" t="s">
+      <c r="A48" s="103" t="s">
         <v>295</v>
       </c>
-      <c r="B48" s="103" t="s">
+      <c r="B48" s="104" t="s">
         <v>296</v>
       </c>
-      <c r="C48" s="104" t="s">
+      <c r="C48" s="105" t="s">
         <v>297</v>
       </c>
       <c r="D48" s="73"/>
@@ -6789,13 +6804,13 @@
       <c r="I48" s="73"/>
     </row>
     <row r="49" ht="42" customHeight="1" spans="1:9">
-      <c r="A49" s="105" t="s">
+      <c r="A49" s="106" t="s">
         <v>298</v>
       </c>
-      <c r="B49" s="106" t="s">
+      <c r="B49" s="107" t="s">
         <v>299</v>
       </c>
-      <c r="C49" s="107" t="s">
+      <c r="C49" s="108" t="s">
         <v>300</v>
       </c>
       <c r="D49" s="73"/>
@@ -6806,13 +6821,13 @@
       <c r="I49" s="73"/>
     </row>
     <row r="50" ht="42" customHeight="1" spans="1:9">
-      <c r="A50" s="108" t="s">
+      <c r="A50" s="109" t="s">
         <v>301</v>
       </c>
-      <c r="B50" s="109" t="s">
+      <c r="B50" s="110" t="s">
         <v>302</v>
       </c>
-      <c r="C50" s="110" t="s">
+      <c r="C50" s="111" t="s">
         <v>303</v>
       </c>
       <c r="D50" s="73"/>
@@ -6861,13 +6876,13 @@
       <c r="A54" s="78" t="s">
         <v>306</v>
       </c>
-      <c r="B54" s="111" t="s">
+      <c r="B54" s="112" t="s">
         <v>307</v>
       </c>
-      <c r="C54" s="111" t="s">
+      <c r="C54" s="112" t="s">
         <v>308</v>
       </c>
-      <c r="D54" s="112" t="s">
+      <c r="D54" s="113" t="s">
         <v>309</v>
       </c>
       <c r="E54" s="73"/>
@@ -6880,13 +6895,13 @@
       <c r="A55" s="81" t="s">
         <v>310</v>
       </c>
-      <c r="B55" s="113" t="s">
+      <c r="B55" s="114" t="s">
         <v>311</v>
       </c>
-      <c r="C55" s="113" t="s">
+      <c r="C55" s="114" t="s">
         <v>312</v>
       </c>
-      <c r="D55" s="114" t="s">
+      <c r="D55" s="115" t="s">
         <v>313</v>
       </c>
       <c r="E55" s="73"/>
@@ -6899,13 +6914,13 @@
       <c r="A56" s="81" t="s">
         <v>314</v>
       </c>
-      <c r="B56" s="113" t="s">
+      <c r="B56" s="114" t="s">
         <v>315</v>
       </c>
-      <c r="C56" s="113" t="s">
+      <c r="C56" s="114" t="s">
         <v>308</v>
       </c>
-      <c r="D56" s="114" t="s">
+      <c r="D56" s="115" t="s">
         <v>316</v>
       </c>
       <c r="E56" s="73"/>
@@ -6918,13 +6933,13 @@
       <c r="A57" s="81" t="s">
         <v>317</v>
       </c>
-      <c r="B57" s="113" t="s">
+      <c r="B57" s="114" t="s">
         <v>318</v>
       </c>
-      <c r="C57" s="113" t="s">
+      <c r="C57" s="114" t="s">
         <v>319</v>
       </c>
-      <c r="D57" s="114" t="s">
+      <c r="D57" s="115" t="s">
         <v>320</v>
       </c>
       <c r="E57" s="73"/>
@@ -6937,13 +6952,13 @@
       <c r="A58" s="81" t="s">
         <v>321</v>
       </c>
-      <c r="B58" s="113" t="s">
+      <c r="B58" s="114" t="s">
         <v>322</v>
       </c>
-      <c r="C58" s="113" t="s">
+      <c r="C58" s="114" t="s">
         <v>323</v>
       </c>
-      <c r="D58" s="114" t="s">
+      <c r="D58" s="115" t="s">
         <v>324</v>
       </c>
       <c r="E58" s="73"/>
@@ -6956,13 +6971,13 @@
       <c r="A59" s="81" t="s">
         <v>325</v>
       </c>
-      <c r="B59" s="113" t="s">
+      <c r="B59" s="114" t="s">
         <v>326</v>
       </c>
-      <c r="C59" s="113" t="s">
+      <c r="C59" s="114" t="s">
         <v>323</v>
       </c>
-      <c r="D59" s="114" t="s">
+      <c r="D59" s="115" t="s">
         <v>327</v>
       </c>
       <c r="E59" s="73"/>
@@ -6975,13 +6990,13 @@
       <c r="A60" s="83" t="s">
         <v>328</v>
       </c>
-      <c r="B60" s="115" t="s">
+      <c r="B60" s="116" t="s">
         <v>329</v>
       </c>
-      <c r="C60" s="115" t="s">
+      <c r="C60" s="116" t="s">
         <v>330</v>
       </c>
-      <c r="D60" s="116" t="s">
+      <c r="D60" s="117" t="s">
         <v>331</v>
       </c>
       <c r="E60" s="73"/>
@@ -7002,17 +7017,17 @@
       <c r="I61" s="73"/>
     </row>
     <row r="62" spans="1:9">
-      <c r="A62" s="117" t="s">
+      <c r="A62" s="118" t="s">
         <v>332</v>
       </c>
-      <c r="B62" s="117"/>
-      <c r="C62" s="117"/>
-      <c r="D62" s="117"/>
-      <c r="E62" s="117"/>
-      <c r="F62" s="117"/>
-      <c r="G62" s="117"/>
-      <c r="H62" s="117"/>
-      <c r="I62" s="117"/>
+      <c r="B62" s="118"/>
+      <c r="C62" s="118"/>
+      <c r="D62" s="118"/>
+      <c r="E62" s="118"/>
+      <c r="F62" s="118"/>
+      <c r="G62" s="118"/>
+      <c r="H62" s="118"/>
+      <c r="I62" s="118"/>
     </row>
     <row r="63" ht="30" customHeight="1" spans="1:9">
       <c r="A63" s="74" t="s">
@@ -7029,10 +7044,10 @@
       <c r="A64" s="78" t="s">
         <v>335</v>
       </c>
-      <c r="B64" s="118" t="s">
+      <c r="B64" s="119" t="s">
         <v>249</v>
       </c>
-      <c r="C64" s="119" t="s">
+      <c r="C64" s="120" t="s">
         <v>336</v>
       </c>
       <c r="D64" s="73"/>
@@ -7046,10 +7061,10 @@
       <c r="A65" s="81" t="s">
         <v>337</v>
       </c>
-      <c r="B65" s="95" t="s">
+      <c r="B65" s="96" t="s">
         <v>292</v>
       </c>
-      <c r="C65" s="120" t="s">
+      <c r="C65" s="121" t="s">
         <v>338</v>
       </c>
       <c r="D65" s="73"/>
@@ -7063,10 +7078,10 @@
       <c r="A66" s="81" t="s">
         <v>339</v>
       </c>
-      <c r="B66" s="95" t="s">
+      <c r="B66" s="96" t="s">
         <v>308</v>
       </c>
-      <c r="C66" s="120" t="s">
+      <c r="C66" s="121" t="s">
         <v>340</v>
       </c>
       <c r="D66" s="73"/>
@@ -7080,10 +7095,10 @@
       <c r="A67" s="81" t="s">
         <v>341</v>
       </c>
-      <c r="B67" s="95" t="s">
+      <c r="B67" s="96" t="s">
         <v>342</v>
       </c>
-      <c r="C67" s="120" t="s">
+      <c r="C67" s="121" t="s">
         <v>343</v>
       </c>
       <c r="D67" s="73"/>
@@ -7097,10 +7112,10 @@
       <c r="A68" s="81" t="s">
         <v>344</v>
       </c>
-      <c r="B68" s="95" t="s">
+      <c r="B68" s="96" t="s">
         <v>319</v>
       </c>
-      <c r="C68" s="120" t="s">
+      <c r="C68" s="121" t="s">
         <v>345</v>
       </c>
       <c r="D68" s="73"/>
@@ -7114,10 +7129,10 @@
       <c r="A69" s="83" t="s">
         <v>346</v>
       </c>
-      <c r="B69" s="121" t="s">
+      <c r="B69" s="122" t="s">
         <v>330</v>
       </c>
-      <c r="C69" s="122" t="s">
+      <c r="C69" s="123" t="s">
         <v>347</v>
       </c>
       <c r="D69" s="73"/>
